--- a/event_planner_forms/008_graduation_guest_book_form--event_planner_forms.xlsx
+++ b/event_planner_forms/008_graduation_guest_book_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>What is your last name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>graduation_message</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>A personal message for the graduate?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>graduation_date</t>
+          <t>When was your graduation?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>graduation_time</t>
+          <t>What time is your graduation?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>graduation_year</t>
+          <t>What is your graduation year?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>graduation_day_of_week</t>
+          <t>Which day of the week is your graduation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>graduation_month</t>
+          <t>Which month is your graduation?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>graduation_year</t>
+          <t>graduation_class_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>graduation_year</t>
+          <t>What is your graduation class name?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,133 +727,87 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>class_name</t>
+          <t>school_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>class_name</t>
+          <t>What school did you attend?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>graduation_day</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>school_name</t>
+          <t>Which day is your graduation day?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>graduation_day_of_week</t>
+          <t>graduation_class_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>graduation_day_of_week</t>
+          <t>Graduation Class Name 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>graduation_month</t>
+          <t>graduation_school_name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>graduation_month</t>
+          <t>What school did you graduate from?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>graduation_day</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>graduation_day</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>graduation_year</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>graduation_year</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1219,406 +1173,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>graduation_day_of_week_choices</t>
+          <t>graduation_day_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>first</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>First</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>graduation_day_of_week_choices</t>
+          <t>graduation_day_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>second</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Second</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>graduation_day_of_week_choices</t>
+          <t>graduation_day_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>third</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Third</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>graduation_day_of_week_choices</t>
+          <t>graduation_day_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>fourth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Fourth</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>graduation_day_of_week_choices</t>
+          <t>graduation_day_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>fifth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>graduation_day_of_week_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>saturday</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>graduation_day_of_week_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>january</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>february</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>February</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>march</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>March</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>april</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>may</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>june</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>July</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>august</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>August</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>september</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>october</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>november</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>graduation_month_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>december</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>graduation_day_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>first</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>graduation_day_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>second</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Second</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>graduation_day_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>third</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Third</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>graduation_day_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>fourth</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Fourth</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>graduation_day_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>fifth</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>Fifth</t>
         </is>
